--- a/public/import/Template soal CBT Essay.xlsx
+++ b/public/import/Template soal CBT Essay.xlsx
@@ -7,15 +7,15 @@
     <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Template Essay" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="20">
   <si>
     <t>Prodi</t>
   </si>
@@ -41,34 +41,40 @@
     <t>Deskripsi Soal</t>
   </si>
   <si>
+    <t>URL Gambar Soal</t>
+  </si>
+  <si>
     <t>Jawaban Referensi</t>
   </si>
   <si>
-    <t>Teknik Informatika</t>
-  </si>
-  <si>
-    <t>Topik Contoh</t>
-  </si>
-  <si>
-    <t>Materi Contoh</t>
-  </si>
-  <si>
-    <t>Sub Materi</t>
-  </si>
-  <si>
-    <t>Essay</t>
-  </si>
-  <si>
-    <t>Kategori Contoh</t>
-  </si>
-  <si>
-    <t>Apa perbedaaan Laravel dan CodeIgniter?</t>
-  </si>
-  <si>
-    <t>Deskripsi soal...</t>
-  </si>
-  <si>
-    <t>Logika Jawaban...</t>
+    <t>URL Gambar Jawaban</t>
+  </si>
+  <si>
+    <t>Kedokteran</t>
+  </si>
+  <si>
+    <t>Sistem Pernapasan</t>
+  </si>
+  <si>
+    <t>Materi 1</t>
+  </si>
+  <si>
+    <t>PMB</t>
+  </si>
+  <si>
+    <t>Jelaskan fungsi dari paru-paru!</t>
+  </si>
+  <si>
+    <t>Jawab dengan singkat dan jelas.</t>
+  </si>
+  <si>
+    <t>https://procbt.id/storage/question/sample.jpg</t>
+  </si>
+  <si>
+    <t>Fungsi utama paru-paru adalah untuk menukar oksigen dari udara dengan karbon dioksida dari darah.</t>
+  </si>
+  <si>
+    <t>https://procbt.id/storage/question/sample_jawaban.jpg</t>
   </si>
 </sst>
 </file>
@@ -408,10 +414,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -439,25 +445,31 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
         <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
@@ -467,6 +479,12 @@
       </c>
       <c r="I2" t="s">
         <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
